--- a/database/controller_excel/Resguardo_Darwin_Ruiz_Aguilar.xlsx
+++ b/database/controller_excel/Resguardo_Darwin_Ruiz_Aguilar.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>05/05/2025</t>
+    <t>08/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Norte</t>
+    <t>Sur</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Cristobal Soto Escalante</t>
-  </si>
-  <si>
-    <t>Auxiliar de Supervision</t>
+    <t>Abraham Palayot Sanchez</t>
+  </si>
+  <si>
+    <t>Informacion Financiera</t>
   </si>
 </sst>
 </file>

--- a/database/controller_excel/Resguardo_Darwin_Ruiz_Aguilar.xlsx
+++ b/database/controller_excel/Resguardo_Darwin_Ruiz_Aguilar.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>08/05/2025</t>
+    <t>13/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -98,6 +98,9 @@
     <t>18-12-27171</t>
   </si>
   <si>
+    <t>ola</t>
+  </si>
+  <si>
     <t>Mochila</t>
   </si>
   <si>
@@ -149,10 +152,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Abraham Palayot Sanchez</t>
-  </si>
-  <si>
-    <t>Informacion Financiera</t>
+    <t>Alejandro Cancino Arguello</t>
+  </si>
+  <si>
+    <t>Coordinador de TI</t>
   </si>
 </sst>
 </file>
@@ -984,7 +987,9 @@
         <v>25</v>
       </c>
       <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
+      <c r="H19" s="38" t="s">
+        <v>26</v>
+      </c>
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
@@ -992,17 +997,17 @@
         <v>2</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E20" s="38"/>
       <c r="F20" s="38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G20" s="38"/>
       <c r="H20" s="38"/>
@@ -1013,17 +1018,17 @@
         <v>3</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E21" s="38"/>
       <c r="F21" s="38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
@@ -1053,7 +1058,7 @@
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
       <c r="A24" s="26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="26"/>
@@ -1077,7 +1082,7 @@
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
       <c r="A26" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="28"/>
       <c r="C26" s="28"/>
@@ -1090,7 +1095,7 @@
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
       <c r="A27" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27" s="28"/>
       <c r="C27" s="28"/>
@@ -1103,7 +1108,7 @@
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
       <c r="A28" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28" s="28"/>
       <c r="C28" s="28"/>
@@ -1116,7 +1121,7 @@
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="24.05">
       <c r="A29" s="29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
@@ -1130,7 +1135,7 @@
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="27">
       <c r="A30" s="28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" s="28"/>
       <c r="C30" s="28"/>
@@ -1154,7 +1159,7 @@
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="39">
       <c r="A32" s="31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" s="31"/>
       <c r="C32" s="31"/>
@@ -1190,14 +1195,14 @@
     <row r="35" spans="1:10" customHeight="1" ht="15">
       <c r="A35" s="32"/>
       <c r="B35" s="34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C35" s="34"/>
       <c r="D35" s="34"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H35" s="35"/>
       <c r="I35" s="35"/>
@@ -1207,7 +1212,7 @@
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
@@ -1240,7 +1245,7 @@
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="2"/>
       <c r="B39" s="34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C39" s="34"/>
       <c r="D39" s="34"/>
@@ -1256,7 +1261,7 @@
     <row r="40" spans="1:10" customHeight="1" ht="15">
       <c r="A40" s="2"/>
       <c r="B40" s="34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C40" s="34"/>
       <c r="D40" s="34"/>

--- a/database/controller_excel/Resguardo_Darwin_Ruiz_Aguilar.xlsx
+++ b/database/controller_excel/Resguardo_Darwin_Ruiz_Aguilar.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>13/05/2025</t>
+    <t>21/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -98,7 +98,7 @@
     <t>18-12-27171</t>
   </si>
   <si>
-    <t>ola</t>
+    <t>dfdfd</t>
   </si>
   <si>
     <t>Mochila</t>
@@ -120,6 +120,27 @@
   </si>
   <si>
     <t>607P283</t>
+  </si>
+  <si>
+    <t>ACCESSPOINT</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>sdcsa</t>
+  </si>
+  <si>
+    <t>ASDSDS</t>
+  </si>
+  <si>
+    <t>Backpack DELL</t>
+  </si>
+  <si>
+    <t>fd</t>
+  </si>
+  <si>
+    <t>FDF</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -1035,80 +1056,96 @@
       <c r="I21" s="38"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
+      <c r="A22" s="38">
+        <v>4</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="15">
-      <c r="A23" s="25"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
+      <c r="A23" s="38">
+        <v>5</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
-      <c r="A24" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
-      <c r="A25" s="27"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
+      <c r="A26" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
+      <c r="A27" s="27"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
       <c r="A28" s="28" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B28" s="28"/>
       <c r="C28" s="28"/>
@@ -1119,23 +1156,22 @@
       <c r="H28" s="28"/>
       <c r="I28" s="28"/>
     </row>
-    <row r="29" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A29" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="2"/>
-    </row>
-    <row r="30" spans="1:10" customHeight="1" ht="27">
+    <row r="29" spans="1:10" customHeight="1" ht="15">
+      <c r="A29" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+    </row>
+    <row r="30" spans="1:10" customHeight="1" ht="15">
       <c r="A30" s="28" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B30" s="28"/>
       <c r="C30" s="28"/>
@@ -1146,96 +1182,101 @@
       <c r="H30" s="28"/>
       <c r="I30" s="28"/>
     </row>
-    <row r="31" spans="1:10" customHeight="1" ht="15">
-      <c r="A31" s="30"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-    </row>
-    <row r="32" spans="1:10" customHeight="1" ht="39">
-      <c r="A32" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
+    <row r="31" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A31" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="2"/>
+    </row>
+    <row r="32" spans="1:10" customHeight="1" ht="27">
+      <c r="A32" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="32"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="2"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="39">
+      <c r="A34" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
       <c r="A35" s="32"/>
-      <c r="B35" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="H35" s="35"/>
-      <c r="I35" s="35"/>
+      <c r="G35" s="33"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33"/>
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
       <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="36" t="s">
-        <v>43</v>
-      </c>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="2"/>
-      <c r="B37" s="37"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
+      <c r="A37" s="32"/>
+      <c r="B37" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="37"/>
+      <c r="G37" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
+      <c r="D38" s="36" t="s">
+        <v>50</v>
+      </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -1244,68 +1285,90 @@
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="2"/>
-      <c r="B39" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="34" t="str">
+      <c r="G39" s="37"/>
+      <c r="H39" s="37"/>
+      <c r="I39" s="37"/>
+    </row>
+    <row r="40" spans="1:10" customHeight="1" ht="15">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+    </row>
+    <row r="41" spans="1:10" customHeight="1" ht="15">
+      <c r="A41" s="2"/>
+      <c r="B41" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="34" t="str">
         <f>C10</f>
         <v>Darwin Ruiz Aguilar</v>
       </c>
-      <c r="H39" s="34"/>
-      <c r="I39" s="34"/>
-    </row>
-    <row r="40" spans="1:10" customHeight="1" ht="15">
-      <c r="A40" s="2"/>
-      <c r="B40" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="34" t="str">
+      <c r="H41" s="34"/>
+      <c r="I41" s="34"/>
+    </row>
+    <row r="42" spans="1:10" customHeight="1" ht="15">
+      <c r="A42" s="2"/>
+      <c r="B42" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="34" t="str">
         <f>C12</f>
         <v>Coordinador de Mantenimiento</v>
       </c>
-      <c r="H40" s="34"/>
-      <c r="I40" s="34"/>
-    </row>
-    <row r="41" spans="1:10" customHeight="1" ht="15">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="32"/>
-    </row>
-    <row r="42" spans="1:10" customHeight="1" ht="15">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="34"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
-      <c r="A43" s="32"/>
-      <c r="B43" s="32"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+    </row>
+    <row r="44" spans="1:10" customHeight="1" ht="15">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+    </row>
+    <row r="45" spans="1:10" customHeight="1" ht="15">
+      <c r="A45" s="32"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1324,23 +1387,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="H24:I24"/>
     <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A32:I32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="G42:I42"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1350,7 +1413,13 @@
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H19:I21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H19:I23"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Darwin_Ruiz_Aguilar.xlsx
+++ b/database/controller_excel/Resguardo_Darwin_Ruiz_Aguilar.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="52">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>21/05/2025</t>
+    <t>02/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Sur</t>
+    <t>Norte</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -98,9 +98,6 @@
     <t>18-12-27171</t>
   </si>
   <si>
-    <t>dfdfd</t>
-  </si>
-  <si>
     <t>Mochila</t>
   </si>
   <si>
@@ -173,10 +170,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Alejandro Cancino Arguello</t>
-  </si>
-  <si>
-    <t>Coordinador de TI</t>
+    <t>Cristobal Soto Escalante</t>
+  </si>
+  <si>
+    <t>Coordinador de Proyectos</t>
   </si>
 </sst>
 </file>
@@ -1008,9 +1005,7 @@
         <v>25</v>
       </c>
       <c r="G19" s="38"/>
-      <c r="H19" s="38" t="s">
-        <v>26</v>
-      </c>
+      <c r="H19" s="38"/>
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
@@ -1018,17 +1013,17 @@
         <v>2</v>
       </c>
       <c r="B20" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="D20" s="38" t="s">
         <v>28</v>
-      </c>
-      <c r="D20" s="38" t="s">
-        <v>29</v>
       </c>
       <c r="E20" s="38"/>
       <c r="F20" s="38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G20" s="38"/>
       <c r="H20" s="38"/>
@@ -1039,17 +1034,17 @@
         <v>3</v>
       </c>
       <c r="B21" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="D21" s="38" t="s">
         <v>31</v>
-      </c>
-      <c r="D21" s="38" t="s">
-        <v>32</v>
       </c>
       <c r="E21" s="38"/>
       <c r="F21" s="38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
@@ -1060,17 +1055,17 @@
         <v>4</v>
       </c>
       <c r="B22" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="D22" s="38" t="s">
         <v>35</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>36</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G22" s="38"/>
       <c r="H22" s="38"/>
@@ -1081,17 +1076,17 @@
         <v>5</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1121,7 +1116,7 @@
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
       <c r="A26" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="26"/>
@@ -1145,7 +1140,7 @@
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
       <c r="A28" s="28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="28"/>
       <c r="C28" s="28"/>
@@ -1158,7 +1153,7 @@
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
       <c r="A29" s="28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" s="28"/>
       <c r="C29" s="28"/>
@@ -1171,7 +1166,7 @@
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
       <c r="A30" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B30" s="28"/>
       <c r="C30" s="28"/>
@@ -1184,7 +1179,7 @@
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="24.05">
       <c r="A31" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B31" s="29"/>
       <c r="C31" s="29"/>
@@ -1198,7 +1193,7 @@
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="27">
       <c r="A32" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -1222,7 +1217,7 @@
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="39">
       <c r="A34" s="31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
@@ -1258,14 +1253,14 @@
     <row r="37" spans="1:10" customHeight="1" ht="15">
       <c r="A37" s="32"/>
       <c r="B37" s="34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C37" s="34"/>
       <c r="D37" s="34"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H37" s="35"/>
       <c r="I37" s="35"/>
@@ -1275,7 +1270,7 @@
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -1308,7 +1303,7 @@
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="2"/>
       <c r="B41" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41" s="34"/>
       <c r="D41" s="34"/>
@@ -1324,7 +1319,7 @@
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="2"/>
       <c r="B42" s="34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="34"/>
       <c r="D42" s="34"/>

--- a/database/controller_excel/Resguardo_Darwin_Ruiz_Aguilar.xlsx
+++ b/database/controller_excel/Resguardo_Darwin_Ruiz_Aguilar.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="52">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,19 +41,19 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>01/07/2025</t>
+    <t>16/07/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>das</t>
+    <t>re</t>
   </si>
   <si>
     <t>Región:</t>
   </si>
   <si>
-    <t>Norte</t>
+    <t>Sur</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -80,10 +80,25 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>Latitude 5520</t>
+  </si>
+  <si>
+    <t>1446MG00C698</t>
+  </si>
+  <si>
+    <t>Y8GS78BY8</t>
+  </si>
+  <si>
     <t>Cargador de Laptop</t>
   </si>
   <si>
-    <t>Tesla</t>
+    <t>HP</t>
   </si>
   <si>
     <t>LA65NM190</t>
@@ -116,9 +131,6 @@
     <t>Monitor</t>
   </si>
   <si>
-    <t>DELL</t>
-  </si>
-  <si>
     <t>E2720HS</t>
   </si>
   <si>
@@ -152,10 +164,10 @@
     <t>ACEPTA Y RECIBE:</t>
   </si>
   <si>
-    <t>Cristobal Soto Escalante</t>
-  </si>
-  <si>
-    <t>Coordinador de Proyectos</t>
+    <t>Alejandro Cancino Arguello</t>
+  </si>
+  <si>
+    <t>Coordinador de TI</t>
   </si>
   <si>
     <t>Coordinador de Mantenimiento</t>
@@ -825,7 +837,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -1069,22 +1081,14 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="52"/>
-      <c r="B18" s="53">
-        <v>2</v>
-      </c>
-      <c r="C18" s="53" t="s">
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="53" t="s">
-        <v>27</v>
-      </c>
       <c r="F18" s="53"/>
-      <c r="G18" s="53" t="s">
-        <v>28</v>
-      </c>
+      <c r="G18" s="53"/>
       <c r="H18" s="53"/>
       <c r="I18" s="53"/>
       <c r="J18" s="53"/>
@@ -1093,20 +1097,20 @@
     <row r="19" spans="1:11">
       <c r="A19" s="52"/>
       <c r="B19" s="53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F19" s="53"/>
       <c r="G19" s="53" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
@@ -1116,92 +1120,112 @@
     <row r="20" spans="1:11">
       <c r="A20" s="52"/>
       <c r="B20" s="53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="53" t="s">
         <v>32</v>
-      </c>
-      <c r="D20" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="53" t="s">
-        <v>34</v>
       </c>
       <c r="F20" s="53"/>
       <c r="G20" s="53" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H20" s="53"/>
       <c r="I20" s="53"/>
       <c r="J20" s="53"/>
       <c r="K20" s="17"/>
     </row>
-    <row r="21" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A21" s="18"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="31"/>
-    </row>
-    <row r="22" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A22" s="18"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="31"/>
+    <row r="21" spans="1:11">
+      <c r="A21" s="52"/>
+      <c r="B21" s="53">
+        <v>4</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="17"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="52"/>
+      <c r="B22" s="53">
+        <v>5</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="17"/>
     </row>
     <row r="23" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="31"/>
     </row>
     <row r="24" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A24" s="19"/>
-      <c r="B24" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-    </row>
-    <row r="25" spans="1:11" customHeight="1" ht="9">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="31"/>
+    </row>
+    <row r="25" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A26" s="20"/>
-      <c r="B26" s="27" t="s">
-        <v>37</v>
+      <c r="A26" s="19"/>
+      <c r="B26" s="33" t="s">
+        <v>40</v>
       </c>
       <c r="C26" s="26"/>
       <c r="D26" s="26"/>
@@ -1212,24 +1236,22 @@
       <c r="I26" s="26"/>
       <c r="J26" s="26"/>
     </row>
-    <row r="27" spans="1:11" customHeight="1" ht="15">
+    <row r="27" spans="1:11" customHeight="1" ht="9">
       <c r="A27" s="20"/>
-      <c r="B27" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-    </row>
-    <row r="28" spans="1:11" customHeight="1" ht="15">
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+    </row>
+    <row r="28" spans="1:11" customHeight="1" ht="15.75">
       <c r="A28" s="20"/>
       <c r="B28" s="27" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C28" s="26"/>
       <c r="D28" s="26"/>
@@ -1243,7 +1265,7 @@
     <row r="29" spans="1:11" customHeight="1" ht="15">
       <c r="A29" s="20"/>
       <c r="B29" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C29" s="26"/>
       <c r="D29" s="26"/>
@@ -1257,7 +1279,7 @@
     <row r="30" spans="1:11" customHeight="1" ht="15">
       <c r="A30" s="20"/>
       <c r="B30" s="27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C30" s="26"/>
       <c r="D30" s="26"/>
@@ -1268,9 +1290,11 @@
       <c r="I30" s="26"/>
       <c r="J30" s="26"/>
     </row>
-    <row r="31" spans="1:11" customHeight="1" ht="12">
-      <c r="A31" s="21"/>
-      <c r="B31" s="28"/>
+    <row r="31" spans="1:11" customHeight="1" ht="15">
+      <c r="A31" s="20"/>
+      <c r="B31" s="27" t="s">
+        <v>44</v>
+      </c>
       <c r="C31" s="26"/>
       <c r="D31" s="26"/>
       <c r="E31" s="26"/>
@@ -1280,10 +1304,10 @@
       <c r="I31" s="26"/>
       <c r="J31" s="26"/>
     </row>
-    <row r="32" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A32" s="17"/>
-      <c r="B32" s="29" t="s">
-        <v>42</v>
+    <row r="32" spans="1:11" customHeight="1" ht="15">
+      <c r="A32" s="20"/>
+      <c r="B32" s="27" t="s">
+        <v>45</v>
       </c>
       <c r="C32" s="26"/>
       <c r="D32" s="26"/>
@@ -1294,84 +1318,130 @@
       <c r="I32" s="26"/>
       <c r="J32" s="26"/>
     </row>
-    <row r="33" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-    </row>
-    <row r="34" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
+    <row r="33" spans="1:11" customHeight="1" ht="12">
+      <c r="A33" s="21"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+    </row>
+    <row r="34" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A34" s="17"/>
+      <c r="B34" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="26"/>
     </row>
     <row r="35" spans="1:11" customHeight="1" ht="15.75">
       <c r="A35" s="22"/>
       <c r="B35" s="22"/>
-      <c r="C35" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="H35" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-    </row>
-    <row r="36" spans="1:11" customHeight="1" ht="15.75"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+    </row>
+    <row r="36" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+    </row>
     <row r="37" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
-      <c r="J37" s="23"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="H37" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
     </row>
     <row r="38" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="39" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C39" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="H39" s="25" t="str">
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="23"/>
+    </row>
+    <row r="40" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="41" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C41" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="H41" s="25" t="str">
         <f>C8</f>
         <v>Darwin Ruiz Aguilar</v>
       </c>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-    </row>
-    <row r="40" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C40" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="H40" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-    </row>
-    <row r="41" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-    </row>
-    <row r="42" spans="1:11" customHeight="1" ht="15.75"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+    </row>
+    <row r="42" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C42" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="H42" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+    </row>
     <row r="43" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A43" s="22"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="22"/>
+    </row>
+    <row r="44" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="45" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="F47" s="22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="F51" s="22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="F52" s="22" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>
@@ -1386,26 +1456,26 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
     <mergeCell ref="B26:J26"/>
-    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="H42:J42"/>
     <mergeCell ref="B28:J28"/>
     <mergeCell ref="B29:J29"/>
     <mergeCell ref="B30:J30"/>
     <mergeCell ref="B31:J31"/>
     <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B33:J33"/>
+    <mergeCell ref="B34:J34"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
@@ -1418,7 +1488,13 @@
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I17:J20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I17:J22"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>
